--- a/AI_Stock.xlsx
+++ b/AI_Stock.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tora\Documents\Investering\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16811A69-FB94-41A9-9072-189CFBDF92C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B04D997D-91DB-4AA0-B2ED-FE3148A510E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{1F7F3BB6-0204-4628-AFD5-3B370F61661C}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{1F7F3BB6-0204-4628-AFD5-3B370F61661C}"/>
   </bookViews>
   <sheets>
     <sheet name="Aktier" sheetId="1" r:id="rId1"/>
@@ -652,7 +652,7 @@
     <col min="2" max="2" width="14.7265625" customWidth="1"/>
     <col min="3" max="5" width="14.26953125" customWidth="1"/>
     <col min="6" max="6" width="22.36328125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="7.453125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.90625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="7.453125" customWidth="1"/>
     <col min="9" max="9" width="17.453125" bestFit="1" customWidth="1"/>
   </cols>
@@ -694,19 +694,19 @@
         <v>50</v>
       </c>
       <c r="C2">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D2" s="2">
-        <v>809</v>
+        <v>818.77</v>
       </c>
       <c r="E2" s="2">
-        <v>986</v>
+        <v>948.6</v>
       </c>
       <c r="F2" s="1">
-        <v>22776.600000000002</v>
-      </c>
-      <c r="G2" s="4">
-        <v>0.17951318458417853</v>
+        <v>23164.812000000005</v>
+      </c>
+      <c r="G2" s="1">
+        <v>3170.448600000007</v>
       </c>
       <c r="H2" s="4" t="s">
         <v>65</v>
@@ -729,13 +729,13 @@
         <v>436.48</v>
       </c>
       <c r="E3" s="2">
-        <v>540</v>
+        <v>513.5</v>
       </c>
       <c r="F3" s="1">
-        <v>27000</v>
-      </c>
-      <c r="G3" s="4">
-        <v>0.19170370370370371</v>
+        <v>25675</v>
+      </c>
+      <c r="G3" s="1">
+        <v>3170.448600000007</v>
       </c>
       <c r="H3" s="4" t="s">
         <v>66</v>
@@ -752,19 +752,19 @@
         <v>52</v>
       </c>
       <c r="C4">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="D4" s="2">
-        <v>149.29</v>
+        <v>163</v>
       </c>
       <c r="E4" s="2">
-        <v>151</v>
+        <v>131.30000000000001</v>
       </c>
       <c r="F4" s="1">
-        <v>12341.23</v>
-      </c>
-      <c r="G4" s="4">
-        <v>1.1324503311258338E-2</v>
+        <v>4877.7950000000001</v>
+      </c>
+      <c r="G4" s="1">
+        <v>-1177.6549999999997</v>
       </c>
       <c r="H4" s="4" t="s">
         <v>67</v>
@@ -787,13 +787,13 @@
         <v>1018.6</v>
       </c>
       <c r="E5" s="2">
-        <v>1385</v>
+        <v>1514.6</v>
       </c>
       <c r="F5" s="1">
-        <v>51452.75</v>
-      </c>
-      <c r="G5" s="4">
-        <v>0.26454873646209387</v>
+        <v>56267.39</v>
+      </c>
+      <c r="G5" s="1">
+        <v>18426.400000000001</v>
       </c>
       <c r="H5" s="4" t="s">
         <v>67</v>
@@ -816,13 +816,13 @@
         <v>200.43</v>
       </c>
       <c r="E6" s="2">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="F6" s="1">
-        <v>50949</v>
-      </c>
-      <c r="G6" s="4">
-        <v>0.39810810810810804</v>
+        <v>50337</v>
+      </c>
+      <c r="G6" s="1">
+        <v>19671.21</v>
       </c>
       <c r="H6" s="4" t="s">
         <v>66</v>
@@ -845,13 +845,13 @@
         <v>10.725</v>
       </c>
       <c r="E7" s="2">
-        <v>11.6</v>
+        <v>11.27</v>
       </c>
       <c r="F7" s="1">
-        <v>12893.98</v>
-      </c>
-      <c r="G7" s="4">
-        <v>7.5431034482758674E-2</v>
+        <v>12527.168499999998</v>
+      </c>
+      <c r="G7" s="1">
+        <v>605.79474999999729</v>
       </c>
       <c r="H7" s="4" t="s">
         <v>69</v>
@@ -868,19 +868,19 @@
         <v>57</v>
       </c>
       <c r="C8">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D8" s="2">
-        <v>389.49</v>
+        <v>388</v>
       </c>
       <c r="E8" s="2">
-        <v>368.35</v>
+        <v>345.3</v>
       </c>
       <c r="F8" s="1">
-        <v>33424.079000000005</v>
-      </c>
-      <c r="G8" s="4">
-        <v>-5.7391068277453439E-2</v>
+        <v>35918.106</v>
+      </c>
+      <c r="G8" s="1">
+        <v>-4441.6540000000023</v>
       </c>
       <c r="H8" s="4" t="s">
         <v>67</v>
@@ -903,13 +903,13 @@
         <v>403.53</v>
       </c>
       <c r="E9" s="2">
-        <v>1057</v>
+        <v>963.5</v>
       </c>
       <c r="F9" s="1">
-        <v>75047</v>
-      </c>
-      <c r="G9" s="4">
-        <v>0.61823084200567646</v>
+        <v>68408.5</v>
+      </c>
+      <c r="G9" s="1">
+        <v>39757.870000000003</v>
       </c>
       <c r="H9" s="4" t="s">
         <v>66</v>
@@ -932,13 +932,13 @@
         <v>426.68</v>
       </c>
       <c r="E10" s="2">
-        <v>294.10000000000002</v>
+        <v>278</v>
       </c>
       <c r="F10" s="1">
-        <v>98817.600000000006</v>
-      </c>
-      <c r="G10" s="4">
-        <v>-0.45079904794287651</v>
+        <v>93408</v>
+      </c>
+      <c r="G10" s="1">
+        <v>-42214.569999999992</v>
       </c>
       <c r="H10" s="4" t="s">
         <v>66</v>
@@ -961,13 +961,13 @@
         <v>610.35</v>
       </c>
       <c r="E11" s="2">
-        <v>600</v>
+        <v>614</v>
       </c>
       <c r="F11" s="1">
-        <v>19200</v>
-      </c>
-      <c r="G11" s="4">
-        <v>-1.7249999999999988E-2</v>
+        <v>19648</v>
+      </c>
+      <c r="G11" s="1">
+        <v>116.79999999999927</v>
       </c>
       <c r="H11" s="4" t="s">
         <v>66</v>
@@ -984,19 +984,19 @@
         <v>60</v>
       </c>
       <c r="C12">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="D12" s="2">
-        <v>155.62</v>
+        <v>144.16999999999999</v>
       </c>
       <c r="E12" s="2">
-        <v>168.7</v>
+        <v>139.63999999999999</v>
       </c>
       <c r="F12" s="1">
-        <v>22561.937999999998</v>
-      </c>
-      <c r="G12" s="4">
-        <v>7.7534084173088269E-2</v>
+        <v>9337.7267999999985</v>
+      </c>
+      <c r="G12" s="1">
+        <v>-302.92110000000139</v>
       </c>
       <c r="H12" s="4" t="s">
         <v>67</v>
@@ -1013,19 +1013,19 @@
         <v>61</v>
       </c>
       <c r="C13">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D13" s="2">
-        <v>360</v>
+        <v>384.47</v>
       </c>
       <c r="E13" s="2">
-        <v>422.22</v>
+        <v>413.255</v>
       </c>
       <c r="F13" s="1">
-        <v>28233.851400000003</v>
-      </c>
-      <c r="G13" s="4">
-        <v>0.14736393349438692</v>
+        <v>46057.269749999999</v>
+      </c>
+      <c r="G13" s="1">
+        <v>3208.0882500000007</v>
       </c>
       <c r="H13" s="4" t="s">
         <v>68</v>
@@ -1048,13 +1048,13 @@
         <v>307.14999999999998</v>
       </c>
       <c r="E14" s="2">
-        <v>327.39999999999998</v>
+        <v>350.8</v>
       </c>
       <c r="F14" s="1">
-        <v>12162.91</v>
-      </c>
-      <c r="G14" s="4">
-        <v>6.1850946854001276E-2</v>
+        <v>13032.22</v>
+      </c>
+      <c r="G14" s="1">
+        <v>1621.5974999999999</v>
       </c>
       <c r="H14" s="4" t="s">
         <v>67</v>
@@ -1071,19 +1071,19 @@
         <v>63</v>
       </c>
       <c r="C15">
-        <v>134</v>
+        <v>108</v>
       </c>
       <c r="D15" s="2">
-        <v>148.30000000000001</v>
+        <v>145.84</v>
       </c>
       <c r="E15" s="2">
-        <v>175.95</v>
+        <v>166</v>
       </c>
       <c r="F15" s="1">
-        <v>23577.3</v>
-      </c>
-      <c r="G15" s="4">
-        <v>0.15714691673770942</v>
+        <v>17928</v>
+      </c>
+      <c r="G15" s="1">
+        <v>2177.2799999999988</v>
       </c>
       <c r="H15" s="4" t="s">
         <v>66</v>

--- a/AI_Stock.xlsx
+++ b/AI_Stock.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tora\Documents\Investering\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B04D997D-91DB-4AA0-B2ED-FE3148A510E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BB50567-AF60-4899-BCD5-DC66FC734321}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{1F7F3BB6-0204-4628-AFD5-3B370F61661C}"/>
   </bookViews>
@@ -204,18 +204,9 @@
     <t>DANSKE:XCSE</t>
   </si>
   <si>
-    <t>NOVO:XCSE</t>
-  </si>
-  <si>
-    <t>IVN:NEOE</t>
-  </si>
-  <si>
     <t>MSF:XETR</t>
   </si>
   <si>
-    <t>NKT:XCSE</t>
-  </si>
-  <si>
     <t>PNDORA:XCSE</t>
   </si>
   <si>
@@ -253,6 +244,15 @@
   </si>
   <si>
     <t>Købskurs</t>
+  </si>
+  <si>
+    <t>NKT:CO</t>
+  </si>
+  <si>
+    <t>NOVO-B:CO</t>
+  </si>
+  <si>
+    <t>IVN:TO</t>
   </si>
 </sst>
 </file>
@@ -668,10 +668,10 @@
         <v>1</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="F1" s="3" t="s">
         <v>49</v>
@@ -680,7 +680,7 @@
         <v>2</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="I1" s="3" t="s">
         <v>0</v>
@@ -709,7 +709,7 @@
         <v>3170.448600000007</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="I2" s="1" t="s">
         <v>17</v>
@@ -738,7 +738,7 @@
         <v>3170.448600000007</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="I3" s="1" t="s">
         <v>18</v>
@@ -767,7 +767,7 @@
         <v>-1177.6549999999997</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="I4" s="1" t="s">
         <v>19</v>
@@ -796,7 +796,7 @@
         <v>18426.400000000001</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="I5" s="1" t="s">
         <v>20</v>
@@ -825,7 +825,7 @@
         <v>19671.21</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="I6" s="1" t="s">
         <v>18</v>
@@ -836,7 +836,7 @@
         <v>16</v>
       </c>
       <c r="B7" t="s">
-        <v>56</v>
+        <v>71</v>
       </c>
       <c r="C7">
         <v>215</v>
@@ -854,7 +854,7 @@
         <v>605.79474999999729</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="I7" s="1" t="s">
         <v>19</v>
@@ -865,7 +865,7 @@
         <v>9</v>
       </c>
       <c r="B8" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C8">
         <v>14</v>
@@ -883,7 +883,7 @@
         <v>-4441.6540000000023</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="I8" s="1" t="s">
         <v>20</v>
@@ -894,7 +894,7 @@
         <v>10</v>
       </c>
       <c r="B9" t="s">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="C9">
         <v>71</v>
@@ -912,7 +912,7 @@
         <v>39757.870000000003</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="I9" s="1" t="s">
         <v>21</v>
@@ -923,7 +923,7 @@
         <v>11</v>
       </c>
       <c r="B10" t="s">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="C10">
         <v>336</v>
@@ -941,7 +941,7 @@
         <v>-42214.569999999992</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="I10" s="1" t="s">
         <v>22</v>
@@ -952,7 +952,7 @@
         <v>12</v>
       </c>
       <c r="B11" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="C11">
         <v>32</v>
@@ -970,7 +970,7 @@
         <v>116.79999999999927</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="I11" s="1" t="s">
         <v>23</v>
@@ -981,7 +981,7 @@
         <v>8</v>
       </c>
       <c r="B12" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="C12">
         <v>9</v>
@@ -999,7 +999,7 @@
         <v>-302.92110000000139</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="I12" s="1" t="s">
         <v>17</v>
@@ -1010,7 +1010,7 @@
         <v>13</v>
       </c>
       <c r="B13" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="C13">
         <v>15</v>
@@ -1028,7 +1028,7 @@
         <v>3208.0882500000007</v>
       </c>
       <c r="H13" s="4" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="I13" s="1" t="s">
         <v>20</v>
@@ -1039,7 +1039,7 @@
         <v>14</v>
       </c>
       <c r="B14" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C14">
         <v>5</v>
@@ -1057,7 +1057,7 @@
         <v>1621.5974999999999</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="I14" s="1" t="s">
         <v>22</v>
@@ -1068,7 +1068,7 @@
         <v>15</v>
       </c>
       <c r="B15" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="C15">
         <v>108</v>
@@ -1086,7 +1086,7 @@
         <v>2177.2799999999988</v>
       </c>
       <c r="H15" s="4" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="I15" s="1" t="s">
         <v>24</v>

--- a/AI_Stock.xlsx
+++ b/AI_Stock.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tora\Documents\Investering\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BB50567-AF60-4899-BCD5-DC66FC734321}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74167940-6199-480A-B344-B90F05BE079C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{1F7F3BB6-0204-4628-AFD5-3B370F61661C}"/>
+    <workbookView xWindow="-57705" yWindow="0" windowWidth="14610" windowHeight="17385" xr2:uid="{1F7F3BB6-0204-4628-AFD5-3B370F61661C}"/>
   </bookViews>
   <sheets>
     <sheet name="Aktier" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="72">
   <si>
     <t>Sektor</t>
   </si>
@@ -192,67 +192,67 @@
     <t>ABB:XSTO</t>
   </si>
   <si>
+    <t>ASML:XAMS</t>
+  </si>
+  <si>
+    <t>DANSKE:XCSE</t>
+  </si>
+  <si>
+    <t>MSF:XETR</t>
+  </si>
+  <si>
+    <t>PNDORA:XCSE</t>
+  </si>
+  <si>
+    <t>ENR:XETR</t>
+  </si>
+  <si>
+    <t>TSM:XNYS</t>
+  </si>
+  <si>
+    <t>UNH:XETR</t>
+  </si>
+  <si>
+    <t>VWS:XCSE</t>
+  </si>
+  <si>
+    <t>Valuta</t>
+  </si>
+  <si>
+    <t>SEK</t>
+  </si>
+  <si>
+    <t>DKK</t>
+  </si>
+  <si>
+    <t>EUR</t>
+  </si>
+  <si>
+    <t>USD</t>
+  </si>
+  <si>
+    <t>Aktuel kurs</t>
+  </si>
+  <si>
+    <t>Købskurs</t>
+  </si>
+  <si>
+    <t>NKT.CO</t>
+  </si>
+  <si>
+    <t>NOVO-B.CO</t>
+  </si>
+  <si>
+    <t>Frontline plc</t>
+  </si>
+  <si>
+    <t>FRO</t>
+  </si>
+  <si>
+    <t>AL Sydbank</t>
+  </si>
+  <si>
     <t>ALSYDB:XCSE</t>
-  </si>
-  <si>
-    <t>AMC:XETR</t>
-  </si>
-  <si>
-    <t>ASML:XAMS</t>
-  </si>
-  <si>
-    <t>DANSKE:XCSE</t>
-  </si>
-  <si>
-    <t>MSF:XETR</t>
-  </si>
-  <si>
-    <t>PNDORA:XCSE</t>
-  </si>
-  <si>
-    <t>ENR:XETR</t>
-  </si>
-  <si>
-    <t>TSM:XNYS</t>
-  </si>
-  <si>
-    <t>UNH:XETR</t>
-  </si>
-  <si>
-    <t>VWS:XCSE</t>
-  </si>
-  <si>
-    <t>Valuta</t>
-  </si>
-  <si>
-    <t>SEK</t>
-  </si>
-  <si>
-    <t>DKK</t>
-  </si>
-  <si>
-    <t>EUR</t>
-  </si>
-  <si>
-    <t>USD</t>
-  </si>
-  <si>
-    <t>CAD</t>
-  </si>
-  <si>
-    <t>Aktuel kurs</t>
-  </si>
-  <si>
-    <t>Købskurs</t>
-  </si>
-  <si>
-    <t>NKT:CO</t>
-  </si>
-  <si>
-    <t>NOVO-B:CO</t>
-  </si>
-  <si>
-    <t>IVN:TO</t>
   </si>
 </sst>
 </file>
@@ -645,7 +645,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E9FDDCB4-212A-42D6-97A8-2A9AAEE3ECA2}">
-  <dimension ref="A1:I15"/>
+  <dimension ref="A1:I14"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="39.81640625" bestFit="1" customWidth="1"/>
@@ -668,10 +668,10 @@
         <v>1</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="F1" s="3" t="s">
         <v>49</v>
@@ -680,7 +680,7 @@
         <v>2</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="I1" s="3" t="s">
         <v>0</v>
@@ -694,22 +694,22 @@
         <v>50</v>
       </c>
       <c r="C2">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="D2" s="2">
-        <v>818.77</v>
+        <v>858.39</v>
       </c>
       <c r="E2" s="2">
-        <v>948.6</v>
+        <v>985</v>
       </c>
       <c r="F2" s="1">
-        <v>23164.812000000005</v>
+        <v>31485.300000000003</v>
       </c>
       <c r="G2" s="1">
-        <v>3170.448600000007</v>
+        <v>4858.0421999999999</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="I2" s="1" t="s">
         <v>17</v>
@@ -717,378 +717,349 @@
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>4</v>
+        <v>70</v>
       </c>
       <c r="B3" t="s">
-        <v>51</v>
+        <v>71</v>
       </c>
       <c r="C3">
         <v>50</v>
       </c>
       <c r="D3" s="2">
-        <v>436.48</v>
+        <v>438</v>
       </c>
       <c r="E3" s="2">
-        <v>513.5</v>
+        <v>604</v>
       </c>
       <c r="F3" s="1">
-        <v>25675</v>
+        <v>30050</v>
       </c>
       <c r="G3" s="1">
-        <v>3170.448600000007</v>
+        <v>8150</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C4">
         <v>5</v>
       </c>
       <c r="D4" s="2">
-        <v>163</v>
+        <v>1020</v>
       </c>
       <c r="E4" s="2">
-        <v>131.30000000000001</v>
+        <v>1530</v>
       </c>
       <c r="F4" s="1">
-        <v>4877.7950000000001</v>
+        <v>58214.049999999996</v>
       </c>
       <c r="G4" s="1">
-        <v>-1177.6549999999997</v>
+        <v>20321.049999999996</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C5">
-        <v>5</v>
+        <v>153</v>
       </c>
       <c r="D5" s="2">
-        <v>1018.6</v>
+        <v>200.43</v>
       </c>
       <c r="E5" s="2">
-        <v>1514.6</v>
+        <v>367.8</v>
       </c>
       <c r="F5" s="1">
-        <v>56267.39</v>
+        <v>56548.800000000003</v>
       </c>
       <c r="G5" s="1">
-        <v>18426.400000000001</v>
+        <v>25883.010000000002</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>7</v>
+        <v>68</v>
       </c>
       <c r="B6" t="s">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="C6">
-        <v>153</v>
+        <v>22</v>
       </c>
       <c r="D6" s="2">
-        <v>200.43</v>
+        <v>40.619999999999997</v>
       </c>
       <c r="E6" s="2">
-        <v>329</v>
+        <v>38.909999999999997</v>
       </c>
       <c r="F6" s="1">
-        <v>50337</v>
+        <v>11019.953100000001</v>
       </c>
       <c r="G6" s="1">
-        <v>19671.21</v>
+        <v>-750.50429999999687</v>
       </c>
       <c r="H6" s="4" t="s">
         <v>63</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="B7" t="s">
-        <v>71</v>
+        <v>53</v>
       </c>
       <c r="C7">
-        <v>215</v>
+        <v>14</v>
       </c>
       <c r="D7" s="2">
-        <v>10.725</v>
+        <v>390</v>
       </c>
       <c r="E7" s="2">
-        <v>11.27</v>
+        <v>340.7</v>
       </c>
       <c r="F7" s="1">
-        <v>12527.168499999998</v>
+        <v>34945.519</v>
       </c>
       <c r="G7" s="1">
-        <v>605.79474999999729</v>
+        <v>-5622.2809999999954</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B8" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="C8">
-        <v>14</v>
+        <v>63</v>
       </c>
       <c r="D8" s="2">
-        <v>388</v>
+        <v>405.68</v>
       </c>
       <c r="E8" s="2">
-        <v>345.3</v>
+        <v>935</v>
       </c>
       <c r="F8" s="1">
-        <v>35918.106</v>
+        <v>59220</v>
       </c>
       <c r="G8" s="1">
-        <v>-4441.6540000000023</v>
+        <v>33662.160000000003</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B9" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C9">
-        <v>71</v>
+        <v>336</v>
       </c>
       <c r="D9" s="2">
-        <v>403.53</v>
+        <v>426.68</v>
       </c>
       <c r="E9" s="2">
-        <v>963.5</v>
+        <v>321.60000000000002</v>
       </c>
       <c r="F9" s="1">
-        <v>68408.5</v>
+        <v>107570.4</v>
       </c>
       <c r="G9" s="1">
-        <v>39757.870000000003</v>
+        <v>-32140.720000000001</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B10" t="s">
-        <v>70</v>
+        <v>54</v>
       </c>
       <c r="C10">
-        <v>336</v>
+        <v>38</v>
       </c>
       <c r="D10" s="2">
-        <v>426.68</v>
+        <v>631.61</v>
       </c>
       <c r="E10" s="2">
-        <v>278</v>
+        <v>762.4</v>
       </c>
       <c r="F10" s="1">
-        <v>93408</v>
+        <v>29533.600000000002</v>
       </c>
       <c r="G10" s="1">
-        <v>-42214.569999999992</v>
+        <v>5532.4200000000019</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B11" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C11">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="D11" s="2">
-        <v>610.35</v>
+        <v>144</v>
       </c>
       <c r="E11" s="2">
-        <v>614</v>
+        <v>150.76</v>
       </c>
       <c r="F11" s="1">
-        <v>19648</v>
+        <v>10388.923200000001</v>
       </c>
       <c r="G11" s="1">
-        <v>116.79999999999927</v>
+        <v>759.64320000000225</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="B12" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C12">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D12" s="2">
-        <v>144.16999999999999</v>
+        <v>414.2</v>
       </c>
       <c r="E12" s="2">
-        <v>139.63999999999999</v>
+        <v>433.82</v>
       </c>
       <c r="F12" s="1">
-        <v>9337.7267999999985</v>
+        <v>46468.334500000004</v>
       </c>
       <c r="G12" s="1">
-        <v>-302.92110000000139</v>
+        <v>3383.2505000000019</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B13" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C13">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="D13" s="2">
-        <v>384.47</v>
+        <v>322.88</v>
       </c>
       <c r="E13" s="2">
-        <v>413.255</v>
+        <v>375.2</v>
       </c>
       <c r="F13" s="1">
-        <v>46057.269749999999</v>
+        <v>22444.544000000002</v>
       </c>
       <c r="G13" s="1">
-        <v>3208.0882500000007</v>
+        <v>2866.7912000000033</v>
       </c>
       <c r="H13" s="4" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B14" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C14">
-        <v>5</v>
+        <v>108</v>
       </c>
       <c r="D14" s="2">
-        <v>307.14999999999998</v>
+        <v>145.84</v>
       </c>
       <c r="E14" s="2">
-        <v>350.8</v>
+        <v>177</v>
       </c>
       <c r="F14" s="1">
-        <v>13032.22</v>
+        <v>19440</v>
       </c>
       <c r="G14" s="1">
-        <v>1621.5974999999999</v>
+        <v>3689.2799999999988</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A15" t="s">
-        <v>15</v>
-      </c>
-      <c r="B15" t="s">
-        <v>60</v>
-      </c>
-      <c r="C15">
-        <v>108</v>
-      </c>
-      <c r="D15" s="2">
-        <v>145.84</v>
-      </c>
-      <c r="E15" s="2">
-        <v>166</v>
-      </c>
-      <c r="F15" s="1">
-        <v>17928</v>
-      </c>
-      <c r="G15" s="1">
-        <v>2177.2799999999988</v>
-      </c>
-      <c r="H15" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="I15" s="1" t="s">
         <v>24</v>
       </c>
     </row>

--- a/AI_Stock.xlsx
+++ b/AI_Stock.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tora\Documents\Investering\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74167940-6199-480A-B344-B90F05BE079C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5450AF7-1EDE-41F5-A492-08F52358EDA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-57705" yWindow="0" windowWidth="14610" windowHeight="17385" xr2:uid="{1F7F3BB6-0204-4628-AFD5-3B370F61661C}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{1F7F3BB6-0204-4628-AFD5-3B370F61661C}"/>
   </bookViews>
   <sheets>
     <sheet name="Aktier" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="71">
   <si>
     <t>Sektor</t>
   </si>
@@ -94,9 +94,6 @@
   </si>
   <si>
     <t>Finans</t>
-  </si>
-  <si>
-    <t>Materialer</t>
   </si>
   <si>
     <t>Teknologi</t>
@@ -659,28 +656,28 @@
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C1" s="3" t="s">
         <v>1</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G1" s="3" t="s">
         <v>2</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I1" s="3" t="s">
         <v>0</v>
@@ -691,7 +688,7 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C2">
         <v>47</v>
@@ -700,7 +697,7 @@
         <v>858.39</v>
       </c>
       <c r="E2" s="2">
-        <v>985</v>
+        <v>1015</v>
       </c>
       <c r="F2" s="1">
         <v>31485.300000000003</v>
@@ -709,7 +706,7 @@
         <v>4858.0421999999999</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I2" s="1" t="s">
         <v>17</v>
@@ -717,10 +714,10 @@
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
+        <v>69</v>
+      </c>
+      <c r="B3" t="s">
         <v>70</v>
-      </c>
-      <c r="B3" t="s">
-        <v>71</v>
       </c>
       <c r="C3">
         <v>50</v>
@@ -729,19 +726,19 @@
         <v>438</v>
       </c>
       <c r="E3" s="2">
-        <v>604</v>
+        <v>614</v>
       </c>
       <c r="F3" s="1">
-        <v>30050</v>
+        <v>30700</v>
       </c>
       <c r="G3" s="1">
-        <v>8150</v>
+        <v>8800</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.35">
@@ -749,7 +746,7 @@
         <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C4">
         <v>5</v>
@@ -758,19 +755,19 @@
         <v>1020</v>
       </c>
       <c r="E4" s="2">
-        <v>1530</v>
+        <v>1588</v>
       </c>
       <c r="F4" s="1">
-        <v>58214.049999999996</v>
+        <v>58994.2</v>
       </c>
       <c r="G4" s="1">
-        <v>20321.049999999996</v>
+        <v>21101.199999999997</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.35">
@@ -778,7 +775,7 @@
         <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C5">
         <v>153</v>
@@ -787,16 +784,16 @@
         <v>200.43</v>
       </c>
       <c r="E5" s="2">
-        <v>367.8</v>
+        <v>373</v>
       </c>
       <c r="F5" s="1">
-        <v>56548.800000000003</v>
+        <v>57069</v>
       </c>
       <c r="G5" s="1">
-        <v>25883.010000000002</v>
+        <v>26403.21</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I5" s="1" t="s">
         <v>18</v>
@@ -804,10 +801,10 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
+        <v>67</v>
+      </c>
+      <c r="B6" t="s">
         <v>68</v>
-      </c>
-      <c r="B6" t="s">
-        <v>69</v>
       </c>
       <c r="C6">
         <v>22</v>
@@ -816,19 +813,19 @@
         <v>40.619999999999997</v>
       </c>
       <c r="E6" s="2">
-        <v>38.909999999999997</v>
+        <v>38.1</v>
       </c>
       <c r="F6" s="1">
-        <v>11019.953100000001</v>
+        <v>11040.237000000001</v>
       </c>
       <c r="G6" s="1">
-        <v>-750.50429999999687</v>
+        <v>-730.22039999999652</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.35">
@@ -836,7 +833,7 @@
         <v>9</v>
       </c>
       <c r="B7" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C7">
         <v>14</v>
@@ -845,19 +842,19 @@
         <v>390</v>
       </c>
       <c r="E7" s="2">
-        <v>340.7</v>
+        <v>346.55</v>
       </c>
       <c r="F7" s="1">
-        <v>34945.519</v>
+        <v>36048.130999999994</v>
       </c>
       <c r="G7" s="1">
-        <v>-5622.2809999999954</v>
+        <v>-4519.6690000000017</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.35">
@@ -865,7 +862,7 @@
         <v>10</v>
       </c>
       <c r="B8" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C8">
         <v>63</v>
@@ -874,19 +871,19 @@
         <v>405.68</v>
       </c>
       <c r="E8" s="2">
-        <v>935</v>
+        <v>930</v>
       </c>
       <c r="F8" s="1">
-        <v>59220</v>
+        <v>58590</v>
       </c>
       <c r="G8" s="1">
-        <v>33662.160000000003</v>
+        <v>33032.160000000003</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.35">
@@ -894,7 +891,7 @@
         <v>11</v>
       </c>
       <c r="B9" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C9">
         <v>336</v>
@@ -903,19 +900,19 @@
         <v>426.68</v>
       </c>
       <c r="E9" s="2">
-        <v>321.60000000000002</v>
+        <v>334.2</v>
       </c>
       <c r="F9" s="1">
-        <v>107570.4</v>
+        <v>112291.2</v>
       </c>
       <c r="G9" s="1">
-        <v>-32140.720000000001</v>
+        <v>-28782.76999999999</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.35">
@@ -923,7 +920,7 @@
         <v>12</v>
       </c>
       <c r="B10" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C10">
         <v>38</v>
@@ -932,19 +929,19 @@
         <v>631.61</v>
       </c>
       <c r="E10" s="2">
-        <v>762.4</v>
+        <v>794.8</v>
       </c>
       <c r="F10" s="1">
-        <v>29533.600000000002</v>
+        <v>30202.399999999998</v>
       </c>
       <c r="G10" s="1">
-        <v>5532.4200000000019</v>
+        <v>6201.2199999999975</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.35">
@@ -952,7 +949,7 @@
         <v>8</v>
       </c>
       <c r="B11" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C11">
         <v>9</v>
@@ -961,16 +958,16 @@
         <v>144</v>
       </c>
       <c r="E11" s="2">
-        <v>150.76</v>
+        <v>153.72</v>
       </c>
       <c r="F11" s="1">
-        <v>10388.923200000001</v>
+        <v>10279.2564</v>
       </c>
       <c r="G11" s="1">
-        <v>759.64320000000225</v>
+        <v>649.97640000000138</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="I11" s="1" t="s">
         <v>17</v>
@@ -981,7 +978,7 @@
         <v>13</v>
       </c>
       <c r="B12" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C12">
         <v>14</v>
@@ -990,19 +987,19 @@
         <v>414.2</v>
       </c>
       <c r="E12" s="2">
-        <v>433.82</v>
+        <v>425.75</v>
       </c>
       <c r="F12" s="1">
-        <v>46468.334500000004</v>
+        <v>44286.514999999999</v>
       </c>
       <c r="G12" s="1">
-        <v>3383.2505000000019</v>
+        <v>1201.4309999999969</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.35">
@@ -1010,7 +1007,7 @@
         <v>14</v>
       </c>
       <c r="B13" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C13">
         <v>7</v>
@@ -1019,19 +1016,19 @@
         <v>322.88</v>
       </c>
       <c r="E13" s="2">
-        <v>375.2</v>
+        <v>362.8</v>
       </c>
       <c r="F13" s="1">
-        <v>22444.544000000002</v>
+        <v>21564.831999999999</v>
       </c>
       <c r="G13" s="1">
-        <v>2866.7912000000033</v>
+        <v>1987.0792000000001</v>
       </c>
       <c r="H13" s="4" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.35">
@@ -1039,7 +1036,7 @@
         <v>15</v>
       </c>
       <c r="B14" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C14">
         <v>108</v>
@@ -1051,16 +1048,16 @@
         <v>177</v>
       </c>
       <c r="F14" s="1">
-        <v>19440</v>
+        <v>19116</v>
       </c>
       <c r="G14" s="1">
-        <v>3689.2799999999988</v>
+        <v>3365.2799999999988</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
   </sheetData>
@@ -1083,39 +1080,39 @@
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A1" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1" t="s">
         <v>25</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D1" t="s">
         <v>26</v>
       </c>
-      <c r="C1" t="s">
+      <c r="E1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" t="s">
+        <v>28</v>
+      </c>
+      <c r="G1" t="s">
+        <v>29</v>
+      </c>
+      <c r="H1" t="s">
+        <v>30</v>
+      </c>
+      <c r="I1" t="s">
+        <v>31</v>
+      </c>
+      <c r="J1" t="s">
         <v>33</v>
-      </c>
-      <c r="D1" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1" t="s">
-        <v>28</v>
-      </c>
-      <c r="F1" t="s">
-        <v>29</v>
-      </c>
-      <c r="G1" t="s">
-        <v>30</v>
-      </c>
-      <c r="H1" t="s">
-        <v>31</v>
-      </c>
-      <c r="I1" t="s">
-        <v>32</v>
-      </c>
-      <c r="J1" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B2" t="s">
         <v>3</v>
@@ -1123,7 +1120,7 @@
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A3" s="5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B3" t="s">
         <v>4</v>
@@ -1131,7 +1128,7 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A4" s="5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B4" t="s">
         <v>5</v>
@@ -1139,7 +1136,7 @@
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A5" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B5" t="s">
         <v>6</v>
@@ -1147,7 +1144,7 @@
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A6" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B6" t="s">
         <v>7</v>
@@ -1155,7 +1152,7 @@
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A7" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B7" t="s">
         <v>16</v>
@@ -1163,7 +1160,7 @@
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A8" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B8" t="s">
         <v>9</v>
@@ -1171,7 +1168,7 @@
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A9" s="5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B9" t="s">
         <v>10</v>
@@ -1179,7 +1176,7 @@
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A10" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B10" t="s">
         <v>11</v>
@@ -1187,7 +1184,7 @@
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A11" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B11" t="s">
         <v>12</v>
@@ -1195,7 +1192,7 @@
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A12" s="5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B12" t="s">
         <v>8</v>
@@ -1203,7 +1200,7 @@
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A13" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B13" t="s">
         <v>13</v>
@@ -1211,7 +1208,7 @@
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A14" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B14" t="s">
         <v>14</v>
@@ -1219,7 +1216,7 @@
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A15" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B15" t="s">
         <v>15</v>

--- a/AI_Stock.xlsx
+++ b/AI_Stock.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tora\Documents\Investering\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5450AF7-1EDE-41F5-A492-08F52358EDA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22FBFA1E-B4FC-45C6-8A07-3D72D6393C96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{1F7F3BB6-0204-4628-AFD5-3B370F61661C}"/>
   </bookViews>
@@ -697,13 +697,13 @@
         <v>858.39</v>
       </c>
       <c r="E2" s="2">
-        <v>1015</v>
+        <v>930.2</v>
       </c>
       <c r="F2" s="1">
-        <v>31485.300000000003</v>
+        <v>28854.804000000004</v>
       </c>
       <c r="G2" s="1">
-        <v>4858.0421999999999</v>
+        <v>2227.5462000000007</v>
       </c>
       <c r="H2" s="4" t="s">
         <v>59</v>
@@ -726,13 +726,13 @@
         <v>438</v>
       </c>
       <c r="E3" s="2">
-        <v>614</v>
+        <v>608.5</v>
       </c>
       <c r="F3" s="1">
-        <v>30700</v>
+        <v>30425</v>
       </c>
       <c r="G3" s="1">
-        <v>8800</v>
+        <v>8601</v>
       </c>
       <c r="H3" s="4" t="s">
         <v>60</v>
@@ -755,13 +755,13 @@
         <v>1020</v>
       </c>
       <c r="E4" s="2">
-        <v>1588</v>
+        <v>1536</v>
       </c>
       <c r="F4" s="1">
-        <v>58994.2</v>
+        <v>57062.399999999994</v>
       </c>
       <c r="G4" s="1">
-        <v>21101.199999999997</v>
+        <v>19221.409999999996</v>
       </c>
       <c r="H4" s="4" t="s">
         <v>61</v>
@@ -784,13 +784,13 @@
         <v>200.43</v>
       </c>
       <c r="E5" s="2">
-        <v>373</v>
+        <v>360.1</v>
       </c>
       <c r="F5" s="1">
-        <v>57069</v>
+        <v>55095.3</v>
       </c>
       <c r="G5" s="1">
-        <v>26403.21</v>
+        <v>24470.820000000003</v>
       </c>
       <c r="H5" s="4" t="s">
         <v>60</v>
@@ -813,13 +813,13 @@
         <v>40.619999999999997</v>
       </c>
       <c r="E6" s="2">
-        <v>38.1</v>
+        <v>36.22</v>
       </c>
       <c r="F6" s="1">
-        <v>11040.237000000001</v>
+        <v>10495.4694</v>
       </c>
       <c r="G6" s="1">
-        <v>-730.22039999999652</v>
+        <v>-1274.9879999999976</v>
       </c>
       <c r="H6" s="4" t="s">
         <v>62</v>
@@ -842,13 +842,13 @@
         <v>390</v>
       </c>
       <c r="E7" s="2">
-        <v>346.55</v>
+        <v>343.15</v>
       </c>
       <c r="F7" s="1">
-        <v>36048.130999999994</v>
+        <v>35694.462999999996</v>
       </c>
       <c r="G7" s="1">
-        <v>-4519.6690000000017</v>
+        <v>-4673.6186000000016</v>
       </c>
       <c r="H7" s="4" t="s">
         <v>61</v>
@@ -871,13 +871,13 @@
         <v>405.68</v>
       </c>
       <c r="E8" s="2">
-        <v>930</v>
+        <v>900</v>
       </c>
       <c r="F8" s="1">
-        <v>58590</v>
+        <v>56700</v>
       </c>
       <c r="G8" s="1">
-        <v>33032.160000000003</v>
+        <v>31142.16</v>
       </c>
       <c r="H8" s="4" t="s">
         <v>60</v>
@@ -900,13 +900,13 @@
         <v>426.68</v>
       </c>
       <c r="E9" s="2">
-        <v>334.2</v>
+        <v>336.6</v>
       </c>
       <c r="F9" s="1">
-        <v>112291.2</v>
+        <v>113097.60000000001</v>
       </c>
       <c r="G9" s="1">
-        <v>-28782.76999999999</v>
+        <v>-28209.169999999984</v>
       </c>
       <c r="H9" s="4" t="s">
         <v>60</v>
@@ -929,13 +929,13 @@
         <v>631.61</v>
       </c>
       <c r="E10" s="2">
-        <v>794.8</v>
+        <v>797.8</v>
       </c>
       <c r="F10" s="1">
-        <v>30202.399999999998</v>
+        <v>30316.399999999998</v>
       </c>
       <c r="G10" s="1">
-        <v>6201.2199999999975</v>
+        <v>6315.2199999999975</v>
       </c>
       <c r="H10" s="4" t="s">
         <v>60</v>
@@ -958,13 +958,13 @@
         <v>144</v>
       </c>
       <c r="E11" s="2">
-        <v>153.72</v>
+        <v>142.88</v>
       </c>
       <c r="F11" s="1">
-        <v>10279.2564</v>
+        <v>9554.3855999999996</v>
       </c>
       <c r="G11" s="1">
-        <v>649.97640000000138</v>
+        <v>-86.262300000000323</v>
       </c>
       <c r="H11" s="4" t="s">
         <v>61</v>
@@ -987,13 +987,13 @@
         <v>414.2</v>
       </c>
       <c r="E12" s="2">
-        <v>425.75</v>
+        <v>392.27</v>
       </c>
       <c r="F12" s="1">
-        <v>44286.514999999999</v>
+        <v>40803.9254</v>
       </c>
       <c r="G12" s="1">
-        <v>1201.4309999999969</v>
+        <v>-2281.1586000000025</v>
       </c>
       <c r="H12" s="4" t="s">
         <v>62</v>
@@ -1016,13 +1016,13 @@
         <v>322.88</v>
       </c>
       <c r="E13" s="2">
-        <v>362.8</v>
+        <v>369.6</v>
       </c>
       <c r="F13" s="1">
-        <v>21564.831999999999</v>
+        <v>21969.024000000001</v>
       </c>
       <c r="G13" s="1">
-        <v>1987.0792000000001</v>
+        <v>2391.2712000000029</v>
       </c>
       <c r="H13" s="4" t="s">
         <v>61</v>
@@ -1045,13 +1045,13 @@
         <v>145.84</v>
       </c>
       <c r="E14" s="2">
-        <v>177</v>
+        <v>176.2</v>
       </c>
       <c r="F14" s="1">
-        <v>19116</v>
+        <v>19029.599999999999</v>
       </c>
       <c r="G14" s="1">
-        <v>3365.2799999999988</v>
+        <v>3278.8799999999974</v>
       </c>
       <c r="H14" s="4" t="s">
         <v>60</v>

--- a/AI_Stock.xlsx
+++ b/AI_Stock.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tora\Documents\Investering\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22FBFA1E-B4FC-45C6-8A07-3D72D6393C96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3134133-147F-48AB-B11C-A59F1EFDA751}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{1F7F3BB6-0204-4628-AFD5-3B370F61661C}"/>
   </bookViews>
@@ -697,13 +697,13 @@
         <v>858.39</v>
       </c>
       <c r="E2" s="2">
-        <v>930.2</v>
+        <v>962.2</v>
       </c>
       <c r="F2" s="1">
-        <v>28854.804000000004</v>
+        <v>29847.444000000003</v>
       </c>
       <c r="G2" s="1">
-        <v>2227.5462000000007</v>
+        <v>3220.1862000000001</v>
       </c>
       <c r="H2" s="4" t="s">
         <v>59</v>
@@ -723,16 +723,16 @@
         <v>50</v>
       </c>
       <c r="D3" s="2">
-        <v>438</v>
+        <v>436.48</v>
       </c>
       <c r="E3" s="2">
-        <v>608.5</v>
+        <v>616.5</v>
       </c>
       <c r="F3" s="1">
-        <v>30425</v>
+        <v>30825</v>
       </c>
       <c r="G3" s="1">
-        <v>8601</v>
+        <v>9001</v>
       </c>
       <c r="H3" s="4" t="s">
         <v>60</v>
@@ -752,16 +752,16 @@
         <v>5</v>
       </c>
       <c r="D4" s="2">
-        <v>1020</v>
+        <v>1018.6</v>
       </c>
       <c r="E4" s="2">
-        <v>1536</v>
+        <v>1558</v>
       </c>
       <c r="F4" s="1">
-        <v>57062.399999999994</v>
+        <v>57879.7</v>
       </c>
       <c r="G4" s="1">
-        <v>19221.409999999996</v>
+        <v>20038.71</v>
       </c>
       <c r="H4" s="4" t="s">
         <v>61</v>
@@ -781,16 +781,16 @@
         <v>153</v>
       </c>
       <c r="D5" s="2">
-        <v>200.43</v>
+        <v>200.16</v>
       </c>
       <c r="E5" s="2">
-        <v>360.1</v>
+        <v>366</v>
       </c>
       <c r="F5" s="1">
-        <v>55095.3</v>
+        <v>55998</v>
       </c>
       <c r="G5" s="1">
-        <v>24470.820000000003</v>
+        <v>25373.52</v>
       </c>
       <c r="H5" s="4" t="s">
         <v>60</v>
@@ -813,13 +813,13 @@
         <v>40.619999999999997</v>
       </c>
       <c r="E6" s="2">
-        <v>36.22</v>
+        <v>37.64</v>
       </c>
       <c r="F6" s="1">
-        <v>10495.4694</v>
+        <v>10906.942800000001</v>
       </c>
       <c r="G6" s="1">
-        <v>-1274.9879999999976</v>
+        <v>-863.51459999999679</v>
       </c>
       <c r="H6" s="4" t="s">
         <v>62</v>
@@ -839,16 +839,16 @@
         <v>14</v>
       </c>
       <c r="D7" s="2">
-        <v>390</v>
+        <v>388.08</v>
       </c>
       <c r="E7" s="2">
-        <v>343.15</v>
+        <v>350</v>
       </c>
       <c r="F7" s="1">
-        <v>35694.462999999996</v>
+        <v>36407</v>
       </c>
       <c r="G7" s="1">
-        <v>-4673.6186000000016</v>
+        <v>-3961.0815999999977</v>
       </c>
       <c r="H7" s="4" t="s">
         <v>61</v>
@@ -871,13 +871,13 @@
         <v>405.68</v>
       </c>
       <c r="E8" s="2">
-        <v>900</v>
+        <v>916.5</v>
       </c>
       <c r="F8" s="1">
-        <v>56700</v>
+        <v>57739.5</v>
       </c>
       <c r="G8" s="1">
-        <v>31142.16</v>
+        <v>32181.66</v>
       </c>
       <c r="H8" s="4" t="s">
         <v>60</v>
@@ -900,13 +900,13 @@
         <v>426.68</v>
       </c>
       <c r="E9" s="2">
-        <v>336.6</v>
+        <v>321.39999999999998</v>
       </c>
       <c r="F9" s="1">
-        <v>113097.60000000001</v>
+        <v>107990.39999999999</v>
       </c>
       <c r="G9" s="1">
-        <v>-28209.169999999984</v>
+        <v>-31841.97</v>
       </c>
       <c r="H9" s="4" t="s">
         <v>60</v>
@@ -929,13 +929,13 @@
         <v>631.61</v>
       </c>
       <c r="E10" s="2">
-        <v>797.8</v>
+        <v>759.6</v>
       </c>
       <c r="F10" s="1">
-        <v>30316.399999999998</v>
+        <v>28864.799999999999</v>
       </c>
       <c r="G10" s="1">
-        <v>6315.2199999999975</v>
+        <v>4863.619999999999</v>
       </c>
       <c r="H10" s="4" t="s">
         <v>60</v>
@@ -955,16 +955,16 @@
         <v>9</v>
       </c>
       <c r="D11" s="2">
-        <v>144</v>
+        <v>144.16999999999999</v>
       </c>
       <c r="E11" s="2">
-        <v>142.88</v>
+        <v>157.97999999999999</v>
       </c>
       <c r="F11" s="1">
-        <v>9554.3855999999996</v>
+        <v>10564.122599999999</v>
       </c>
       <c r="G11" s="1">
-        <v>-86.262300000000323</v>
+        <v>923.47469999999885</v>
       </c>
       <c r="H11" s="4" t="s">
         <v>61</v>
@@ -987,13 +987,13 @@
         <v>414.2</v>
       </c>
       <c r="E12" s="2">
-        <v>392.27</v>
+        <v>418.74</v>
       </c>
       <c r="F12" s="1">
-        <v>40803.9254</v>
+        <v>43557.334800000004</v>
       </c>
       <c r="G12" s="1">
-        <v>-2281.1586000000025</v>
+        <v>472.25080000000162</v>
       </c>
       <c r="H12" s="4" t="s">
         <v>62</v>
@@ -1010,19 +1010,19 @@
         <v>56</v>
       </c>
       <c r="C13">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D13" s="2">
-        <v>322.88</v>
+        <v>366.4</v>
       </c>
       <c r="E13" s="2">
-        <v>369.6</v>
+        <v>381.8</v>
       </c>
       <c r="F13" s="1">
-        <v>21969.024000000001</v>
+        <v>22694.191999999999</v>
       </c>
       <c r="G13" s="1">
-        <v>2391.2712000000029</v>
+        <v>3116.4392000000007</v>
       </c>
       <c r="H13" s="4" t="s">
         <v>61</v>
@@ -1045,13 +1045,13 @@
         <v>145.84</v>
       </c>
       <c r="E14" s="2">
-        <v>176.2</v>
+        <v>178.85</v>
       </c>
       <c r="F14" s="1">
-        <v>19029.599999999999</v>
+        <v>19315.8</v>
       </c>
       <c r="G14" s="1">
-        <v>3278.8799999999974</v>
+        <v>3565.0799999999981</v>
       </c>
       <c r="H14" s="4" t="s">
         <v>60</v>

--- a/AI_Stock.xlsx
+++ b/AI_Stock.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tora\Documents\Investering\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3134133-147F-48AB-B11C-A59F1EFDA751}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD7DC5A6-B004-437C-8A7C-4AF6535CF645}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{1F7F3BB6-0204-4628-AFD5-3B370F61661C}"/>
   </bookViews>
@@ -697,13 +697,13 @@
         <v>858.39</v>
       </c>
       <c r="E2" s="2">
-        <v>962.2</v>
+        <v>936</v>
       </c>
       <c r="F2" s="1">
-        <v>29847.444000000003</v>
+        <v>29681.402399999999</v>
       </c>
       <c r="G2" s="1">
-        <v>3220.1862000000001</v>
+        <v>2461.0829489999996</v>
       </c>
       <c r="H2" s="4" t="s">
         <v>59</v>
@@ -726,13 +726,13 @@
         <v>436.48</v>
       </c>
       <c r="E3" s="2">
-        <v>616.5</v>
+        <v>615.5</v>
       </c>
       <c r="F3" s="1">
-        <v>30825</v>
+        <v>30775</v>
       </c>
       <c r="G3" s="1">
-        <v>9001</v>
+        <v>8951</v>
       </c>
       <c r="H3" s="4" t="s">
         <v>60</v>
@@ -755,13 +755,13 @@
         <v>1018.6</v>
       </c>
       <c r="E4" s="2">
-        <v>1558</v>
+        <v>1387</v>
       </c>
       <c r="F4" s="1">
-        <v>57879.7</v>
+        <v>51843.286</v>
       </c>
       <c r="G4" s="1">
-        <v>20038.71</v>
+        <v>13770.055200000003</v>
       </c>
       <c r="H4" s="4" t="s">
         <v>61</v>
@@ -784,13 +784,13 @@
         <v>200.16</v>
       </c>
       <c r="E5" s="2">
-        <v>366</v>
+        <v>364.2</v>
       </c>
       <c r="F5" s="1">
-        <v>55998</v>
+        <v>55722.6</v>
       </c>
       <c r="G5" s="1">
-        <v>25373.52</v>
+        <v>25098.12</v>
       </c>
       <c r="H5" s="4" t="s">
         <v>60</v>
@@ -813,13 +813,13 @@
         <v>40.619999999999997</v>
       </c>
       <c r="E6" s="2">
-        <v>37.64</v>
+        <v>38.296999999999997</v>
       </c>
       <c r="F6" s="1">
-        <v>10906.942800000001</v>
+        <v>11165.429074799998</v>
       </c>
       <c r="G6" s="1">
-        <v>-863.51459999999679</v>
+        <v>-677.26693320000049</v>
       </c>
       <c r="H6" s="4" t="s">
         <v>62</v>
@@ -842,13 +842,13 @@
         <v>388.08</v>
       </c>
       <c r="E7" s="2">
-        <v>350</v>
+        <v>342.9</v>
       </c>
       <c r="F7" s="1">
-        <v>36407</v>
+        <v>35887.365359999996</v>
       </c>
       <c r="G7" s="1">
-        <v>-3961.0815999999977</v>
+        <v>-4728.4665120000063</v>
       </c>
       <c r="H7" s="4" t="s">
         <v>61</v>
@@ -871,13 +871,13 @@
         <v>405.68</v>
       </c>
       <c r="E8" s="2">
-        <v>916.5</v>
+        <v>871</v>
       </c>
       <c r="F8" s="1">
-        <v>57739.5</v>
+        <v>54873</v>
       </c>
       <c r="G8" s="1">
-        <v>32181.66</v>
+        <v>29315.16</v>
       </c>
       <c r="H8" s="4" t="s">
         <v>60</v>
@@ -900,13 +900,13 @@
         <v>426.68</v>
       </c>
       <c r="E9" s="2">
-        <v>321.39999999999998</v>
+        <v>325.89999999999998</v>
       </c>
       <c r="F9" s="1">
-        <v>107990.39999999999</v>
+        <v>109502.39999999999</v>
       </c>
       <c r="G9" s="1">
-        <v>-31841.97</v>
+        <v>-30766.47</v>
       </c>
       <c r="H9" s="4" t="s">
         <v>60</v>
@@ -929,13 +929,13 @@
         <v>631.61</v>
       </c>
       <c r="E10" s="2">
-        <v>759.6</v>
+        <v>782.4</v>
       </c>
       <c r="F10" s="1">
-        <v>28864.799999999999</v>
+        <v>29731.200000000001</v>
       </c>
       <c r="G10" s="1">
-        <v>4863.619999999999</v>
+        <v>5730.02</v>
       </c>
       <c r="H10" s="4" t="s">
         <v>60</v>
@@ -958,13 +958,13 @@
         <v>144.16999999999999</v>
       </c>
       <c r="E11" s="2">
-        <v>157.97999999999999</v>
+        <v>147.12</v>
       </c>
       <c r="F11" s="1">
-        <v>10564.122599999999</v>
+        <v>9898.2924480000001</v>
       </c>
       <c r="G11" s="1">
-        <v>923.47469999999885</v>
+        <v>198.47717999999986</v>
       </c>
       <c r="H11" s="4" t="s">
         <v>61</v>
@@ -987,13 +987,13 @@
         <v>414.2</v>
       </c>
       <c r="E12" s="2">
-        <v>418.74</v>
+        <v>406.07499999999999</v>
       </c>
       <c r="F12" s="1">
-        <v>43557.334800000004</v>
+        <v>42499.159780000002</v>
       </c>
       <c r="G12" s="1">
-        <v>472.25080000000162</v>
+        <v>-850.34949999999662</v>
       </c>
       <c r="H12" s="4" t="s">
         <v>62</v>
@@ -1016,13 +1016,13 @@
         <v>366.4</v>
       </c>
       <c r="E13" s="2">
-        <v>381.8</v>
+        <v>366.6</v>
       </c>
       <c r="F13" s="1">
-        <v>22694.191999999999</v>
+        <v>8221.6648800000021</v>
       </c>
       <c r="G13" s="1">
-        <v>3116.4392000000007</v>
+        <v>834.94976400000178</v>
       </c>
       <c r="H13" s="4" t="s">
         <v>61</v>
@@ -1045,13 +1045,13 @@
         <v>145.84</v>
       </c>
       <c r="E14" s="2">
-        <v>178.85</v>
+        <v>169.4</v>
       </c>
       <c r="F14" s="1">
-        <v>19315.8</v>
+        <v>18295.2</v>
       </c>
       <c r="G14" s="1">
-        <v>3565.0799999999981</v>
+        <v>2544.4799999999996</v>
       </c>
       <c r="H14" s="4" t="s">
         <v>60</v>

--- a/AI_Stock.xlsx
+++ b/AI_Stock.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tora\Documents\Investering\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD7DC5A6-B004-437C-8A7C-4AF6535CF645}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF557344-5D80-4B87-8DC5-8EA7B89A9812}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{1F7F3BB6-0204-4628-AFD5-3B370F61661C}"/>
   </bookViews>
@@ -697,10 +697,10 @@
         <v>858.39</v>
       </c>
       <c r="E2" s="2">
-        <v>936</v>
+        <v>940</v>
       </c>
       <c r="F2" s="1">
-        <v>29681.402399999999</v>
+        <v>29808.245999999999</v>
       </c>
       <c r="G2" s="1">
         <v>2461.0829489999996</v>
@@ -726,10 +726,10 @@
         <v>436.48</v>
       </c>
       <c r="E3" s="2">
-        <v>615.5</v>
+        <v>620</v>
       </c>
       <c r="F3" s="1">
-        <v>30775</v>
+        <v>31000</v>
       </c>
       <c r="G3" s="1">
         <v>8951</v>
@@ -749,16 +749,16 @@
         <v>50</v>
       </c>
       <c r="C4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D4" s="2">
-        <v>1018.6</v>
+        <v>1078.93</v>
       </c>
       <c r="E4" s="2">
-        <v>1387</v>
+        <v>1474</v>
       </c>
       <c r="F4" s="1">
-        <v>51843.286</v>
+        <v>66114.206399999995</v>
       </c>
       <c r="G4" s="1">
         <v>13770.055200000003</v>
@@ -784,10 +784,10 @@
         <v>200.16</v>
       </c>
       <c r="E5" s="2">
-        <v>364.2</v>
+        <v>373.2</v>
       </c>
       <c r="F5" s="1">
-        <v>55722.6</v>
+        <v>57099.6</v>
       </c>
       <c r="G5" s="1">
         <v>25098.12</v>
@@ -813,10 +813,10 @@
         <v>40.619999999999997</v>
       </c>
       <c r="E6" s="2">
-        <v>38.296999999999997</v>
+        <v>38.909999999999997</v>
       </c>
       <c r="F6" s="1">
-        <v>11165.429074799998</v>
+        <v>11344.148243999998</v>
       </c>
       <c r="G6" s="1">
         <v>-677.26693320000049</v>
@@ -842,10 +842,10 @@
         <v>388.08</v>
       </c>
       <c r="E7" s="2">
-        <v>342.9</v>
+        <v>387.95</v>
       </c>
       <c r="F7" s="1">
-        <v>35887.365359999996</v>
+        <v>40602.226280000003</v>
       </c>
       <c r="G7" s="1">
         <v>-4728.4665120000063</v>
@@ -871,10 +871,10 @@
         <v>405.68</v>
       </c>
       <c r="E8" s="2">
-        <v>871</v>
+        <v>905</v>
       </c>
       <c r="F8" s="1">
-        <v>54873</v>
+        <v>57015</v>
       </c>
       <c r="G8" s="1">
         <v>29315.16</v>
@@ -900,10 +900,10 @@
         <v>426.68</v>
       </c>
       <c r="E9" s="2">
-        <v>325.89999999999998</v>
+        <v>329.1</v>
       </c>
       <c r="F9" s="1">
-        <v>109502.39999999999</v>
+        <v>110577.60000000001</v>
       </c>
       <c r="G9" s="1">
         <v>-30766.47</v>
@@ -929,10 +929,10 @@
         <v>631.61</v>
       </c>
       <c r="E10" s="2">
-        <v>782.4</v>
+        <v>795</v>
       </c>
       <c r="F10" s="1">
-        <v>29731.200000000001</v>
+        <v>30210</v>
       </c>
       <c r="G10" s="1">
         <v>5730.02</v>
@@ -952,16 +952,16 @@
         <v>54</v>
       </c>
       <c r="C11">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D11" s="2">
-        <v>144.16999999999999</v>
+        <v>142.44</v>
       </c>
       <c r="E11" s="2">
-        <v>147.12</v>
+        <v>149.12</v>
       </c>
       <c r="F11" s="1">
-        <v>9898.2924480000001</v>
+        <v>15606.660608000002</v>
       </c>
       <c r="G11" s="1">
         <v>198.47717999999986</v>
@@ -987,10 +987,10 @@
         <v>414.2</v>
       </c>
       <c r="E12" s="2">
-        <v>406.07499999999999</v>
+        <v>392.49</v>
       </c>
       <c r="F12" s="1">
-        <v>42499.159780000002</v>
+        <v>41077.375416000003</v>
       </c>
       <c r="G12" s="1">
         <v>-850.34949999999662</v>
@@ -1016,10 +1016,10 @@
         <v>366.4</v>
       </c>
       <c r="E13" s="2">
-        <v>366.6</v>
+        <v>365.8</v>
       </c>
       <c r="F13" s="1">
-        <v>8221.6648800000021</v>
+        <v>8203.7234400000016</v>
       </c>
       <c r="G13" s="1">
         <v>834.94976400000178</v>
@@ -1045,10 +1045,10 @@
         <v>145.84</v>
       </c>
       <c r="E14" s="2">
-        <v>169.4</v>
+        <v>183.9</v>
       </c>
       <c r="F14" s="1">
-        <v>18295.2</v>
+        <v>19861.2</v>
       </c>
       <c r="G14" s="1">
         <v>2544.4799999999996</v>
